--- a/07_Public_Finance/_template_PUBLIC_FINANCE.xlsx
+++ b/07_Public_Finance/_template_PUBLIC_FINANCE.xlsx
@@ -302,76 +302,80 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -630,54 +634,54 @@
   <dimension ref="B2:C8"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -700,92 +704,92 @@
   <dimension ref="B2:D13"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <v>0.6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="8" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="8" t="n">
         <v>0.02</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="9" t="n">
         <f aca="false">IFERROR((C6-C7)/(1+C7)*C5,"-")</f>
         <v>0.0176470588235294</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="11" t="n">
         <f aca="false">IFERROR(C8-C11,"-")</f>
         <v>-0.0176470588235294</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="2" t="str">
+      <c r="C13" s="3" t="str">
         <f aca="false">IFERROR(IF(C8&gt;=C11,"STABILIZING/FALLING","RISING"),"-")</f>
         <v>RISING</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="10" t="s">
         <v>22</v>
       </c>
     </row>
@@ -808,113 +812,113 @@
   <dimension ref="B2:C18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="13" t="n">
         <f aca="false">IFERROR(C5-C6,"-")</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C12" s="13" t="str">
+      <c r="C12" s="14" t="str">
         <f aca="false">IFERROR(C11/C7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="13" t="str">
+      <c r="C13" s="14" t="str">
         <f aca="false">IFERROR(C11/(C7+C8),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="14" t="n">
+      <c r="C16" s="15" t="n">
         <v>1.25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="15" t="str">
+      <c r="C17" s="16" t="str">
         <f aca="false">IFERROR(C12-C16,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="2" t="str">
+      <c r="C18" s="3" t="str">
         <f aca="false">IF(NOT(ISNUMBER(C12)),"-",IF(C12&gt;=C16,"PASS — can issue additional parity debt","FAIL"))</f>
         <v>-</v>
       </c>
@@ -938,104 +942,104 @@
   <dimension ref="B2:F14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="17" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/07_Public_Finance/_template_PUBLIC_FINANCE.xlsx
+++ b/07_Public_Finance/_template_PUBLIC_FINANCE.xlsx
@@ -11,7 +11,10 @@
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Debt Sustainability" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Revenue Bond Coverage" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="RefreshLog" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Additional Bonds Test" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Sources" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Checks" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="RefreshLog" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="114">
   <si>
     <t xml:space="preserve">[ISSUER] — Public Finance Model</t>
   </si>
@@ -55,6 +58,12 @@
     <t xml:space="preserve">Weekly</t>
   </si>
   <si>
+    <t xml:space="preserve">Scenario (Base/Stress):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base</t>
+  </si>
+  <si>
     <t xml:space="preserve">Debt Sustainability Analysis (DSA)</t>
   </si>
   <si>
@@ -118,16 +127,229 @@
     <t xml:space="preserve">All-in DSCR (Net revenue / Total debt service)</t>
   </si>
   <si>
-    <t xml:space="preserve">Additional Bonds Test</t>
+    <t xml:space="preserve">Additional Bonds Test covenant</t>
   </si>
   <si>
     <t xml:space="preserve">ABT minimum senior DSCR covenant</t>
   </si>
   <si>
-    <t xml:space="preserve">Headroom (actual minus covenant)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Passes ABT?</t>
+    <t xml:space="preserve">Current-period headroom (actual minus covenant)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See the 'Additional Bonds Test' sheet for the forward-looking test on a proposed new issuance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional Bonds Test — Proposed New Issuance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A static current-DSCR-vs-covenant check answers 'are we compliant today.' An ABT answers a different question: 'if we issue $X of new parity debt, do we STILL clear covenant' — the actual gate that decides whether a revenue-bond issuer can borrow more.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposed New Issuance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New par amount ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coupon rate on new bonds (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Term of new bonds (years)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New bond level annual debt service (P&amp;I)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumes current-interest, level-debt-service structuring (the standard muni convention) — Excel's native PMT, not a capital-appreciation or non-level schedule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existing Debt Service &amp; Net Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existing senior debt service ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net revenue available for debt service ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historical (Look-Back) Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro-forma total senior debt service ($) = existing + new</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro-forma senior DSCR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Headroom (pro-forma DSCR minus covenant)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historical test result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projected (Look-Forward) Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active scenario (from Cover)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue growth rate — Base (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue growth rate — Stress (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O&amp;M growth rate — Base (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O&amp;M growth rate — Stress (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active revenue growth rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active O&amp;M growth rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O&amp;M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro-forma Senior DS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro-forma DSCR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass/Fail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum projected DSCR (5-yr window)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year of minimum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projected test result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indentures typically require passing the historical OR the projected test (not always both) before additional parity debt may be issued — confirm which applies for a specific issuer's indenture; see model_card.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What each material assumption or convention in this model comes from.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumption / convention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMF Debt Sustainability Analysis (DSA) framework</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard practice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public-domain IMF methodology, not issuer-specific</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Additional Bonds Test: historical + projected look-forward tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Typical municipal revenue-bond indenture additional-parity-debt covenant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual indenture language varies by issuer; implements the common historical-or-projected pattern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New-issuance level debt service (PMT amortization)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard level-debt-service muni bond structuring convention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current-interest, level P&amp;I only — no capital-appreciation or non-level schedules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABT minimum senior DSCR covenant (1.25x default)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[fill in — issuer's actual bond indenture]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[fill in]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Placeholder default; replace with the specific indenture's real covenant level before use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live reconciliation identities -- independent of the model's own formulas, must tie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passes when</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net revenue ties: Gross revenue - O&amp;M = Net revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (exact)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro-forma Yr1 debt service ties: existing + new = pro forma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New-bond PMT reproduces closed-form level-annuity payment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~0 (native PMT matches closed-form annuity formula)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSA trajectory label matches sign of primary-balance gap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
@@ -152,14 +374,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="166" formatCode="0.00%;\(0.00%\);\-"/>
     <numFmt numFmtId="167" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="168" formatCode="0.0\x"/>
+    <numFmt numFmtId="169" formatCode="#,##0;\(#,##0\);\-"/>
+    <numFmt numFmtId="170" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,6 +438,13 @@
       <i val="true"/>
       <sz val="8"/>
       <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -302,7 +533,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -371,11 +602,43 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -631,7 +894,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C8"/>
+  <dimension ref="B2:C9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
@@ -683,6 +946,14 @@
       </c>
       <c r="C8" s="4" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -712,17 +983,17 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>0.6</v>
@@ -730,7 +1001,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>0.05</v>
@@ -738,7 +1009,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>0.02</v>
@@ -746,7 +1017,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>0</v>
@@ -754,43 +1025,43 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C11" s="9" t="n">
         <f aca="false">IFERROR((C6-C7)/(1+C7)*C5,"-")</f>
         <v>0.0176470588235294</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C12" s="11" t="n">
         <f aca="false">IFERROR(C8-C11,"-")</f>
         <v>-0.0176470588235294</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C13" s="3" t="str">
         <f aca="false">IFERROR(IF(C8&gt;=C11,"STABILIZING/FALLING","RISING"),"-")</f>
         <v>RISING</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -820,17 +1091,17 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>0</v>
@@ -838,7 +1109,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>0</v>
@@ -846,7 +1117,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C7" s="12" t="n">
         <v>0</v>
@@ -854,7 +1125,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>0</v>
@@ -862,12 +1133,12 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" s="13" t="n">
         <f aca="false">IFERROR(C5-C6,"-")</f>
@@ -876,7 +1147,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" s="14" t="str">
         <f aca="false">IFERROR(C11/C7,"-")</f>
@@ -885,7 +1156,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C13" s="14" t="str">
         <f aca="false">IFERROR(C11/(C7+C8),"-")</f>
@@ -894,12 +1165,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16" s="15" t="n">
         <v>1.25</v>
@@ -907,7 +1178,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C17" s="16" t="str">
         <f aca="false">IFERROR(C12-C16,"-")</f>
@@ -915,12 +1186,8 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="3" t="str">
-        <f aca="false">IF(NOT(ISNUMBER(C12)),"-",IF(C12&gt;=C16,"PASS — can issue additional parity debt","FAIL"))</f>
-        <v>-</v>
+      <c r="B18" s="10" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -939,6 +1206,621 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:H42"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>20000000</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="17" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <f aca="false">IFERROR(-PMT(C7,C8,C6),"-")</f>
+        <v>1537522.88648096</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <f aca="false">'Revenue Bond Coverage'!C7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <f aca="false">'Revenue Bond Coverage'!C11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="20" t="n">
+        <f aca="false">'Revenue Bond Coverage'!C16</f>
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <f aca="false">C12+C9</f>
+        <v>1537522.88648096</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="14" t="n">
+        <f aca="false">IFERROR(C13/C17,"-")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <f aca="false">IFERROR(C18-C14,"-")</f>
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C20" s="3" t="str">
+        <f aca="false">IF(NOT(ISNUMBER(C18)),"-",IF(C18&gt;=C14,"PASS","FAIL"))</f>
+        <v>FAIL</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="21" t="str">
+        <f aca="false">Cover!C9</f>
+        <v>Base</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="9" t="n">
+        <f aca="false">IF(Cover!$C$9="Stress",C25,C24)</f>
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <f aca="false">IF(Cover!$C$9="Stress",C27,C26)</f>
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F31" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="H31" s="22" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="13" t="n">
+        <f aca="false">'Revenue Bond Coverage'!$C$5*(1+$C$28)</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="13" t="n">
+        <f aca="false">'Revenue Bond Coverage'!$C$6*(1+$C$29)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="13" t="n">
+        <f aca="false">C32-D32</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <f aca="false">$C$17</f>
+        <v>1537522.88648096</v>
+      </c>
+      <c r="G32" s="14" t="n">
+        <f aca="false">IFERROR(E32/F32,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="23" t="str">
+        <f aca="false">IF(G32&gt;=$C$14,"PASS","FAIL")</f>
+        <v>FAIL</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="13" t="n">
+        <f aca="false">C32*(1+$C$28)</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <f aca="false">D32*(1+$C$29)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="13" t="n">
+        <f aca="false">C33-D33</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="13" t="n">
+        <f aca="false">$C$17</f>
+        <v>1537522.88648096</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <f aca="false">IFERROR(E33/F33,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="H33" s="23" t="str">
+        <f aca="false">IF(G33&gt;=$C$14,"PASS","FAIL")</f>
+        <v>FAIL</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C34" s="13" t="n">
+        <f aca="false">C33*(1+$C$28)</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="13" t="n">
+        <f aca="false">D33*(1+$C$29)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <f aca="false">C34-D34</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <f aca="false">$C$17</f>
+        <v>1537522.88648096</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <f aca="false">IFERROR(E34/F34,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="23" t="str">
+        <f aca="false">IF(G34&gt;=$C$14,"PASS","FAIL")</f>
+        <v>FAIL</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="13" t="n">
+        <f aca="false">C34*(1+$C$28)</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="13" t="n">
+        <f aca="false">D34*(1+$C$29)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="13" t="n">
+        <f aca="false">C35-D35</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="13" t="n">
+        <f aca="false">$C$17</f>
+        <v>1537522.88648096</v>
+      </c>
+      <c r="G35" s="14" t="n">
+        <f aca="false">IFERROR(E35/F35,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="H35" s="23" t="str">
+        <f aca="false">IF(G35&gt;=$C$14,"PASS","FAIL")</f>
+        <v>FAIL</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="13" t="n">
+        <f aca="false">C35*(1+$C$28)</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="13" t="n">
+        <f aca="false">D35*(1+$C$29)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <f aca="false">C36-D36</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <f aca="false">$C$17</f>
+        <v>1537522.88648096</v>
+      </c>
+      <c r="G36" s="14" t="n">
+        <f aca="false">IFERROR(E36/F36,"-")</f>
+        <v>0</v>
+      </c>
+      <c r="H36" s="23" t="str">
+        <f aca="false">IF(G36&gt;=$C$14,"PASS","FAIL")</f>
+        <v>FAIL</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C38" s="14" t="n">
+        <f aca="false">MIN(G32:G36)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="23" t="str">
+        <f aca="false">INDEX(B32:B36,MATCH(C38,G32:G36,0))</f>
+        <v>Year 1</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" s="3" t="str">
+        <f aca="false">IF(C38&gt;=C14,"PASS — all 5 years clear covenant","FAIL — covenant breached in "&amp;C39)</f>
+        <v>FAIL — covenant breached in Year 1</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:E9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:D9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="26" t="n">
+        <f aca="false">'Revenue Bond Coverage'!C11-('Revenue Bond Coverage'!C5-'Revenue Bond Coverage'!C6)</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="26" t="n">
+        <f aca="false">'Additional Bonds Test'!C17-('Additional Bonds Test'!C12+'Additional Bonds Test'!C9)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="26" t="n">
+        <f aca="false">'Additional Bonds Test'!C9-('Additional Bonds Test'!C6*'Additional Bonds Test'!C7/(1-(1+'Additional Bonds Test'!C7)^-'Additional Bonds Test'!C8))</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="26" t="b">
+        <f aca="false">IF('Debt Sustainability'!C12&gt;=0,"STABILIZING/FALLING","RISING")='Debt Sustainability'!C13</f>
+        <v>1</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:F14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -951,95 +1833,95 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>35</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="17" t="s">
-        <v>40</v>
+      <c r="B4" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
